--- a/aReport_card/2025_2026/Second_term/JSS1/Second_term_JSS1_PHE.xlsx
+++ b/aReport_card/2025_2026/Second_term/JSS1/Second_term_JSS1_PHE.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{178FA441-C949-48C7-8B7F-3640CE70EA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09271FB8-E685-4F08-8F96-8F11EB07C7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -501,14 +501,12 @@
         <v>34</v>
       </c>
       <c r="D2" s="1">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E2" s="1">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1">
-        <v>77</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -521,14 +519,12 @@
         <v>33</v>
       </c>
       <c r="D3" s="1">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="E3" s="1">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1">
-        <v>76</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -541,14 +537,12 @@
         <v>33</v>
       </c>
       <c r="D4" s="1">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="E4" s="1">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1">
-        <v>76</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
@@ -557,18 +551,12 @@
       <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1">
-        <v>33</v>
-      </c>
-      <c r="D5" s="1">
-        <v>28</v>
-      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
       <c r="E5" s="1">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1">
-        <v>76</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" s="1"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
@@ -581,14 +569,12 @@
         <v>33</v>
       </c>
       <c r="D6" s="1">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="E6" s="1">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1">
-        <v>76</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -601,14 +587,12 @@
         <v>33</v>
       </c>
       <c r="D7" s="1">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E7" s="1">
-        <v>15</v>
-      </c>
-      <c r="F7" s="1">
-        <v>76</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F7" s="1"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -621,14 +605,12 @@
         <v>34</v>
       </c>
       <c r="D8" s="1">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="E8" s="1">
-        <v>15</v>
-      </c>
-      <c r="F8" s="1">
-        <v>77</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
@@ -640,15 +622,11 @@
       <c r="C9" s="1">
         <v>29</v>
       </c>
-      <c r="D9" s="1">
-        <v>28</v>
-      </c>
+      <c r="D9" s="1"/>
       <c r="E9" s="1">
-        <v>15</v>
-      </c>
-      <c r="F9" s="1">
-        <v>72</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
